--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -432,7 +432,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-timing-zeiten}
+    <t xml:space="preserve">Timing {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-timing}
 </t>
   </si>
   <si>
@@ -1255,7 +1255,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="65.23046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:37:50+00:00</t>
+    <t>2026-06-15T21:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$35</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="297">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -291,318 +291,337 @@
     <t>Dosage.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Dosage.extension:DosageCategory</t>
+  </si>
+  <si>
+    <t>DosageCategory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Medikation Extension Dosierungskategorie</t>
+  </si>
+  <si>
+    <t>Dosage.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Dosage.sequence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Die Reihenfolge der Dosierungsanweisungen. Entfällt bei Einzeldosierung.</t>
+  </si>
+  <si>
+    <t>Indicates the order in which the dosage instructions should be applied or interpreted.</t>
+  </si>
+  <si>
+    <t>If the sequence number of multiple Dosages is the same, then it is implied that the instructions are to be treated as concurrent.  If the sequence number is different, then the Dosages are intended to be sequential.</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>TQ1-1</t>
+  </si>
+  <si>
+    <t>Dosage.text</t>
+  </si>
+  <si>
+    <t>Freitext-Dosierungsanweisung, wenn keine strukturierte Angabe möglich ist.</t>
+  </si>
+  <si>
+    <t>Free text dosage instructions e.g. SIG.</t>
+  </si>
+  <si>
+    <t>Free text dosage instructions can be used for cases where the instructions are too complex to code.  The content of this attribute does not include the name or description of the medication. When coded instructions are present, the free text instructions may still be present for display to humans taking or administering the medication. It is expected that the text instructions will always be populated.  If the dosage.timing attribute is also populated, then the dosage.text should reflect the same information as the timing.  Additional information about administration or preparation of the medication should be included as text.</t>
+  </si>
+  <si>
+    <t>RXO-6; RXE-21</t>
+  </si>
+  <si>
+    <t>Dosage.additionalInstruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Codierte Anweisungen oder Warnhinweise für den Patienten, z.B. zur Einnahme oder zur Aufbewahrung des Arzneimittels. (ex):
+https://hl7.org/fhir/R4/valueset-additional-instruction-codes.html.</t>
+  </si>
+  <si>
+    <t>Supplemental instructions to the patient on how to take the medication  (e.g. "with meals" or"take half to one hour before food") or warnings for the patient about the medication (e.g. "may cause drowsiness" or "avoid exposure of skin to direct sunlight or sunlamps").</t>
+  </si>
+  <si>
+    <t>Information about administration or preparation of the medication (e.g. "infuse as rapidly as possibly via intraperitoneal port" or "immediately following drug x") should be populated in dosage.text.</t>
+  </si>
+  <si>
+    <t>Additional instruction is intended to be coded, but where no code exists, the element could include text.  For example, "Swallow with plenty of water" which might or might not be coded.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A coded concept identifying additional instructions such as "take with water" or "avoid operating heavy machinery".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/additional-instruction-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>RXO-7</t>
+  </si>
+  <si>
+    <t>Dosage.patientInstruction</t>
+  </si>
+  <si>
+    <t>Freitext Anweisungen für den Patienten, z.B. zur Einnahme oder zur Aufbewahrung des Arzneimittels.</t>
+  </si>
+  <si>
+    <t>Instructions in terms that are understood by the patient or consumer.</t>
+  </si>
+  <si>
+    <t>Dosage.timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timing {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-timing}
+</t>
+  </si>
+  <si>
+    <t>Zeitpunkt oder Zeitraum der Einnahme des Medikaments. 
+Um widersprüchliche Anweisungen zu vermeiden, ist entweder Dosage.timing oder Dosage.text zu befüllen.</t>
+  </si>
+  <si>
+    <t>When medication should be administered.</t>
+  </si>
+  <si>
+    <t>This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
+  </si>
+  <si>
+    <t>The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>Dosage.asNeeded[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Take "as needed" (for x)</t>
+  </si>
+  <si>
+    <t>Indicates whether the Medication is only taken when needed within a specific dosing schedule (Boolean option), or it indicates the precondition for taking the Medication (CodeableConcept).</t>
+  </si>
+  <si>
+    <t>Can express "as needed" without a reason by setting the Boolean = True.  In this case the CodeableConcept is not populated.  Or you can express "as needed" with a reason by including the CodeableConcept.  In this case the Boolean is assumed to be True.  If you set the Boolean to False, then the dose is given according to the schedule and is not "prn" or "as needed".</t>
+  </si>
+  <si>
+    <t>A coded concept identifying the precondition that should be met or evaluated prior to consuming or administering a medication dose.  For example "pain", "30 minutes prior to sexual intercourse", "on flare-up" etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=PRCN].target[classCode=OBS, moodCode=EVN, code="as needed"].value=boolean or codable concept</t>
+  </si>
+  <si>
+    <t>TQ1-9</t>
+  </si>
+  <si>
+    <t>Dosage.asNeeded[x]:asNeededBoolean</t>
+  </si>
+  <si>
+    <t>asNeededBoolean</t>
+  </si>
+  <si>
+    <t>Bedarfsmedikation: Ja/Nein</t>
+  </si>
+  <si>
+    <t>Dosage.asNeeded[x]:asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>Bedarfsmedikation: Grund für die Bedarfsmedikation</t>
+  </si>
+  <si>
+    <t>Dosage.site</t>
+  </si>
+  <si>
+    <t>Körperstelle, an der das Medikament angewendet wird, z.B. Haut, Auge, Ohr etc.</t>
+  </si>
+  <si>
+    <t>Body site to administer to.</t>
+  </si>
+  <si>
+    <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
+  </si>
+  <si>
+    <t>A coded specification of the anatomic site where the medication first enters the body.</t>
+  </si>
+  <si>
+    <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>.approachSiteCode</t>
+  </si>
+  <si>
+    <t>RXR-2</t>
+  </si>
+  <si>
+    <t>Dosage.route</t>
+  </si>
+  <si>
+    <t>Art der Anwendung der Arznei. (z.B. oral, nasal, intravenös, subkutan). Kann bei codierten Arzneien aus der ASP-Liste entnommen werden.</t>
+  </si>
+  <si>
+    <t>How drug should enter body.</t>
+  </si>
+  <si>
+    <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikationartanwendung</t>
+  </si>
+  <si>
+    <t>.routeCode</t>
+  </si>
+  <si>
+    <t>RXR-1</t>
+  </si>
+  <si>
+    <t>Dosage.method</t>
+  </si>
+  <si>
+    <t>Verabreichungsmethode, z.B. Infusion, Injektion, Tablette, Salbe etc.</t>
+  </si>
+  <si>
+    <t>Technique for administering medication.</t>
+  </si>
+  <si>
+    <t>Terminologies used often pre-coordinate this term with the route and or form of administration.</t>
+  </si>
+  <si>
+    <t>A coded value indicating the method by which the medication is introduced into or onto the body. Most commonly used for injections.  For examples, Slow Push; Deep IV.</t>
+  </si>
+  <si>
+    <t>A coded concept describing the technique by which the medicine is administered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>.doseQuantity</t>
+  </si>
+  <si>
+    <t>RXR-4</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element
+</t>
+  </si>
+  <si>
+    <t>Menge des verabreichten Medikaments</t>
+  </si>
+  <si>
+    <t>The amount of medication administered.</t>
+  </si>
+  <si>
+    <t>TQ1-2</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.id</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.extension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Dosage.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Dosage.sequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer
-</t>
-  </si>
-  <si>
-    <t>Die Reihenfolge der Dosierungsanweisungen. Entfällt bei Einzeldosierung.</t>
-  </si>
-  <si>
-    <t>Indicates the order in which the dosage instructions should be applied or interpreted.</t>
-  </si>
-  <si>
-    <t>If the sequence number of multiple Dosages is the same, then it is implied that the instructions are to be treated as concurrent.  If the sequence number is different, then the Dosages are intended to be sequential.</t>
-  </si>
-  <si>
-    <t>.text</t>
-  </si>
-  <si>
-    <t>TQ1-1</t>
-  </si>
-  <si>
-    <t>Dosage.text</t>
-  </si>
-  <si>
-    <t>Freitext-Dosierungsanweisung, wenn keine strukturierte Angabe möglich ist.</t>
-  </si>
-  <si>
-    <t>Free text dosage instructions e.g. SIG.</t>
-  </si>
-  <si>
-    <t>Free text dosage instructions can be used for cases where the instructions are too complex to code.  The content of this attribute does not include the name or description of the medication. When coded instructions are present, the free text instructions may still be present for display to humans taking or administering the medication. It is expected that the text instructions will always be populated.  If the dosage.timing attribute is also populated, then the dosage.text should reflect the same information as the timing.  Additional information about administration or preparation of the medication should be included as text.</t>
-  </si>
-  <si>
-    <t>RXO-6; RXE-21</t>
-  </si>
-  <si>
-    <t>Dosage.additionalInstruction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Codierte Anweisungen oder Warnhinweise für den Patienten, z.B. zur Einnahme oder zur Aufbewahrung des Arzneimittels. (ex):
-https://hl7.org/fhir/R4/valueset-additional-instruction-codes.html.</t>
-  </si>
-  <si>
-    <t>Supplemental instructions to the patient on how to take the medication  (e.g. "with meals" or"take half to one hour before food") or warnings for the patient about the medication (e.g. "may cause drowsiness" or "avoid exposure of skin to direct sunlight or sunlamps").</t>
-  </si>
-  <si>
-    <t>Information about administration or preparation of the medication (e.g. "infuse as rapidly as possibly via intraperitoneal port" or "immediately following drug x") should be populated in dosage.text.</t>
-  </si>
-  <si>
-    <t>Additional instruction is intended to be coded, but where no code exists, the element could include text.  For example, "Swallow with plenty of water" which might or might not be coded.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>A coded concept identifying additional instructions such as "take with water" or "avoid operating heavy machinery".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/additional-instruction-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>RXO-7</t>
-  </si>
-  <si>
-    <t>Dosage.patientInstruction</t>
-  </si>
-  <si>
-    <t>Freitext Anweisungen für den Patienten, z.B. zur Einnahme oder zur Aufbewahrung des Arzneimittels.</t>
-  </si>
-  <si>
-    <t>Instructions in terms that are understood by the patient or consumer.</t>
-  </si>
-  <si>
-    <t>Dosage.timing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timing {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-timing}
-</t>
-  </si>
-  <si>
-    <t>Zeitpunkt oder Zeitraum der Einnahme des Medikaments. 
-Um widersprüchliche Anweisungen zu vermeiden, ist entweder Dosage.timing oder Dosage.text zu befüllen.</t>
-  </si>
-  <si>
-    <t>When medication should be administered.</t>
-  </si>
-  <si>
-    <t>This attribute might not always be populated while the Dosage.text is expected to be populated.  If both are populated, then the Dosage.text should reflect the content of the Dosage.timing.</t>
-  </si>
-  <si>
-    <t>The timing schedule for giving the medication to the patient. This  data type allows many different expressions. For example: "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".  Sometimes, a rate can imply duration when expressed as total volume / duration (e.g.  500mL/2 hours implies a duration of 2 hours).  However, when rate doesn't imply duration (e.g. 250mL/hour), then the timing.repeat.duration is needed to convey the infuse over time period.</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>Dosage.asNeeded[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Take "as needed" (for x)</t>
-  </si>
-  <si>
-    <t>Indicates whether the Medication is only taken when needed within a specific dosing schedule (Boolean option), or it indicates the precondition for taking the Medication (CodeableConcept).</t>
-  </si>
-  <si>
-    <t>Can express "as needed" without a reason by setting the Boolean = True.  In this case the CodeableConcept is not populated.  Or you can express "as needed" with a reason by including the CodeableConcept.  In this case the Boolean is assumed to be True.  If you set the Boolean to False, then the dose is given according to the schedule and is not "prn" or "as needed".</t>
-  </si>
-  <si>
-    <t>A coded concept identifying the precondition that should be met or evaluated prior to consuming or administering a medication dose.  For example "pain", "30 minutes prior to sexual intercourse", "on flare-up" etc.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=PRCN].target[classCode=OBS, moodCode=EVN, code="as needed"].value=boolean or codable concept</t>
-  </si>
-  <si>
-    <t>TQ1-9</t>
-  </si>
-  <si>
-    <t>Dosage.asNeeded[x]:asNeededBoolean</t>
-  </si>
-  <si>
-    <t>asNeededBoolean</t>
-  </si>
-  <si>
-    <t>Bedarfsmedikation: Ja/Nein</t>
-  </si>
-  <si>
-    <t>Dosage.asNeeded[x]:asNeededCodeableConcept</t>
-  </si>
-  <si>
-    <t>asNeededCodeableConcept</t>
-  </si>
-  <si>
-    <t>Bedarfsmedikation: Grund für die Bedarfsmedikation</t>
-  </si>
-  <si>
-    <t>Dosage.site</t>
-  </si>
-  <si>
-    <t>Körperstelle, an der das Medikament angewendet wird, z.B. Haut, Auge, Ohr etc.</t>
-  </si>
-  <si>
-    <t>Body site to administer to.</t>
-  </si>
-  <si>
-    <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
-  </si>
-  <si>
-    <t>A coded specification of the anatomic site where the medication first enters the body.</t>
-  </si>
-  <si>
-    <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>.approachSiteCode</t>
-  </si>
-  <si>
-    <t>RXR-2</t>
-  </si>
-  <si>
-    <t>Dosage.route</t>
-  </si>
-  <si>
-    <t>Art der Anwendung der Arznei. (z.B. oral, nasal, intravenös, subkutan). Kann bei codierten Arzneien aus der ASP-Liste entnommen werden.</t>
-  </si>
-  <si>
-    <t>How drug should enter body.</t>
-  </si>
-  <si>
-    <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/medikationartanwendung</t>
-  </si>
-  <si>
-    <t>.routeCode</t>
-  </si>
-  <si>
-    <t>RXR-1</t>
-  </si>
-  <si>
-    <t>Dosage.method</t>
-  </si>
-  <si>
-    <t>Verabreichungsmethode, z.B. Infusion, Injektion, Tablette, Salbe etc.</t>
-  </si>
-  <si>
-    <t>Technique for administering medication.</t>
-  </si>
-  <si>
-    <t>Terminologies used often pre-coordinate this term with the route and or form of administration.</t>
-  </si>
-  <si>
-    <t>A coded value indicating the method by which the medication is introduced into or onto the body. Most commonly used for injections.  For examples, Slow Push; Deep IV.</t>
-  </si>
-  <si>
-    <t>A coded concept describing the technique by which the medicine is administered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>.doseQuantity</t>
-  </si>
-  <si>
-    <t>RXR-4</t>
-  </si>
-  <si>
-    <t>Dosage.doseAndRate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Element
-</t>
-  </si>
-  <si>
-    <t>Menge des verabreichten Medikaments</t>
-  </si>
-  <si>
-    <t>The amount of medication administered.</t>
-  </si>
-  <si>
-    <t>TQ1-2</t>
-  </si>
-  <si>
-    <t>Dosage.doseAndRate.id</t>
-  </si>
-  <si>
-    <t>Dosage.doseAndRate.extension</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.type</t>
@@ -1242,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL34"/>
+  <dimension ref="A1:AL35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.88671875" customWidth="true" bestFit="true"/>
@@ -1255,7 +1274,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="65.23046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.05078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1621,11 +1640,11 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>76</v>
@@ -1640,17 +1659,15 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M4" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>94</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>21</v>
@@ -1687,19 +1704,19 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AC4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AD4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AD4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE4" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1711,10 +1728,10 @@
         <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>21</v>
@@ -1722,18 +1739,20 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="D5" t="s" s="2">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>76</v>
@@ -1742,26 +1761,22 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
       </c>
@@ -1809,7 +1824,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -1821,54 +1836,56 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N6" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N6" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O6" t="s" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>21</v>
@@ -1917,33 +1934,33 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1951,32 +1968,32 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>21</v>
@@ -2025,7 +2042,7 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -2040,18 +2057,18 @@
         <v>80</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" hidden="true">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2062,31 +2079,29 @@
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>21</v>
@@ -2111,13 +2126,13 @@
         <v>21</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>21</v>
@@ -2135,13 +2150,13 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
@@ -2150,18 +2165,18 @@
         <v>80</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2172,7 +2187,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2181,19 +2196,23 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P9" t="s" s="2">
         <v>21</v>
       </c>
@@ -2217,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>21</v>
@@ -2241,13 +2260,13 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
@@ -2256,13 +2275,13 @@
         <v>80</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>133</v>
       </c>
@@ -2281,29 +2300,25 @@
         <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2366,18 +2381,18 @@
         <v>80</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" hidden="true">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2391,27 +2406,29 @@
         <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O11" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2435,29 +2452,31 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2472,22 +2491,20 @@
         <v>80</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>21</v>
       </c>
@@ -2499,25 +2516,25 @@
         <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2543,31 +2560,29 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2582,18 +2597,18 @@
         <v>80</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" hidden="true">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>155</v>
@@ -2606,28 +2621,28 @@
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2653,13 +2668,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2677,7 +2692,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2692,10 +2707,10 @@
         <v>80</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -2703,9 +2718,11 @@
         <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
@@ -2714,7 +2731,7 @@
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -2723,23 +2740,21 @@
         <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
       </c>
@@ -2763,13 +2778,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -2787,7 +2802,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2802,18 +2817,18 @@
         <v>80</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2827,26 +2842,28 @@
         <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O15" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -2871,11 +2888,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2893,7 +2912,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2908,18 +2927,18 @@
         <v>80</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2933,28 +2952,26 @@
         <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -2979,13 +2996,11 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3003,7 +3018,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3018,18 +3033,18 @@
         <v>80</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3043,25 +3058,29 @@
         <v>83</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -3085,13 +3104,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3109,13 +3128,13 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
@@ -3124,18 +3143,18 @@
         <v>80</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="18" hidden="true">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3149,22 +3168,22 @@
         <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3215,44 +3234,44 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3264,17 +3283,15 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3311,31 +3328,31 @@
         <v>21</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>88</v>
@@ -3346,21 +3363,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3369,21 +3386,21 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3407,57 +3424,57 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3477,22 +3494,20 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" s="2"/>
+      <c r="O21" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3517,29 +3532,31 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3554,22 +3571,20 @@
         <v>80</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
+      <c r="A22" t="s" s="2">
         <v>203</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>204</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3581,28 +3596,28 @@
         <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="O22" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3639,19 +3654,17 @@
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3666,21 +3679,21 @@
         <v>80</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
@@ -3693,28 +3706,28 @@
         <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3763,7 +3776,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3778,20 +3791,22 @@
         <v>80</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>203</v>
       </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3803,25 +3818,29 @@
         <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>85</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3869,7 +3888,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3881,32 +3900,32 @@
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -3918,17 +3937,15 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>94</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -3965,31 +3982,31 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>88</v>
@@ -4000,21 +4017,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4023,23 +4040,21 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>218</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4075,45 +4090,45 @@
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>223</v>
+        <v>96</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>224</v>
+        <v>88</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4124,80 +4139,80 @@
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4212,18 +4227,18 @@
         <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4234,34 +4249,36 @@
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q28" s="2"/>
+      <c r="Q28" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="R28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4281,11 +4298,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4303,7 +4322,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4318,18 +4337,18 @@
         <v>80</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4349,20 +4368,20 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>249</v>
+        <v>84</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4387,13 +4406,11 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -4411,7 +4428,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4420,24 +4437,24 @@
         <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4457,22 +4474,20 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4521,7 +4536,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4530,24 +4545,24 @@
         <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4567,22 +4582,22 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -4631,7 +4646,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4646,18 +4661,18 @@
         <v>80</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>271</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4677,22 +4692,22 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -4741,7 +4756,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4756,18 +4771,18 @@
         <v>80</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4787,22 +4802,22 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -4851,7 +4866,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4866,18 +4881,18 @@
         <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4897,10 +4912,10 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>288</v>
@@ -4908,9 +4923,11 @@
       <c r="M34" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N34" s="2"/>
+      <c r="N34" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -4959,7 +4976,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -4974,14 +4991,122 @@
         <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
     </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL34">
+  <autoFilter ref="A1:AL35">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4991,7 +5116,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI33">
+  <conditionalFormatting sqref="A2:AI34">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-dosierung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
